--- a/test_files/simscape-Formula-Student-Vehicle-Simscape_TEST/FSAE_Pushrod_Parametry.xlsx
+++ b/test_files/simscape-Formula-Student-Vehicle-Simscape_TEST/FSAE_Pushrod_Parametry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FS\test_files\simscape-Formula-Student-Vehicle-Simscape_TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE0D695-0041-4169-9C99-1A40B55E8A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0921CE-2E28-4BE8-935A-601B9F4270D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8556" yWindow="0" windowWidth="14580" windowHeight="12336" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="1" r:id="rId1"/>
@@ -310,9 +310,6 @@
     <t>Vehicle.Chassis.Body.sAxle2.Value</t>
   </si>
   <si>
-    <t>[-1.53, 0, 0]</t>
-  </si>
-  <si>
     <t>[-2.0 .. -1.3, 0, 0]</t>
   </si>
   <si>
@@ -2068,6 +2065,9 @@
   </si>
   <si>
     <t xml:space="preserve">Maximální hydraulický tlak v brzdovém okruhu přední. </t>
+  </si>
+  <si>
+    <t>[-1.575, 0, 0]</t>
   </si>
 </sst>
 </file>
@@ -2412,18 +2412,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2448,6 +2441,13 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2765,54 +2765,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>638</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="A1" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="4" spans="1:6" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>639</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>640</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="30"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>641</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
+      <c r="B5" s="23" t="s">
+        <v>640</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2838,8 +2838,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>589</v>
+      <c r="A1" s="22" t="s">
+        <v>588</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -2878,8 +2878,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>591</v>
+      <c r="A4" s="21" t="s">
+        <v>590</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>592</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>593</v>
       </c>
       <c r="C5" s="7">
         <v>0.15</v>
@@ -2901,18 +2901,18 @@
         <v>89</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>594</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>597</v>
       </c>
       <c r="C6" s="7">
         <v>0.7</v>
@@ -2921,18 +2921,18 @@
         <v>12</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>600</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>601</v>
       </c>
       <c r="C7" s="7">
         <v>0.5</v>
@@ -2941,18 +2941,18 @@
         <v>12</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>602</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>604</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>605</v>
       </c>
       <c r="C8" s="7">
         <v>4</v>
@@ -2961,18 +2961,18 @@
         <v>12</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>606</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>608</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>609</v>
       </c>
       <c r="C9" s="7">
         <v>1.2500000000000001E-2</v>
@@ -2981,35 +2981,35 @@
         <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>610</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>613</v>
       </c>
       <c r="C10" s="7">
         <v>85</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="F10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>615</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>616</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>618</v>
       </c>
       <c r="C12" s="7">
         <v>0.1</v>
@@ -3031,18 +3031,18 @@
         <v>89</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>619</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>621</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>622</v>
       </c>
       <c r="C13" s="7">
         <v>0.7</v>
@@ -3051,18 +3051,18 @@
         <v>12</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>624</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>625</v>
       </c>
       <c r="C14" s="7">
         <v>0.5</v>
@@ -3071,18 +3071,18 @@
         <v>12</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>627</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>628</v>
       </c>
       <c r="C15" s="7">
         <v>2</v>
@@ -3091,18 +3091,18 @@
         <v>12</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>629</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>631</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>632</v>
       </c>
       <c r="C16" s="7">
         <v>1.2500000000000001E-2</v>
@@ -3111,30 +3111,30 @@
         <v>89</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>634</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>635</v>
       </c>
       <c r="C17" s="7">
         <v>57</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E17" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>636</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -3162,7 +3162,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>83</v>
       </c>
       <c r="B1" s="20"/>
@@ -3202,7 +3202,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="21" t="s">
         <v>85</v>
       </c>
       <c r="B4" s="20"/>
@@ -3225,7 +3225,7 @@
         <v>89</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>90</v>
@@ -3239,53 +3239,53 @@
         <v>92</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>93</v>
+        <v>672</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>90</v>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="C9" s="7">
         <v>1.4379999999999999</v>
@@ -3305,15 +3305,15 @@
         <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>105</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -3323,47 +3323,47 @@
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="C11" s="7">
         <v>250</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
-        <v>113</v>
+      <c r="A13" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -3373,19 +3373,19 @@
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>12</v>
@@ -3393,19 +3393,19 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>12</v>
@@ -3438,8 +3438,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>122</v>
+      <c r="A1" s="22" t="s">
+        <v>121</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -3478,8 +3478,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>124</v>
+      <c r="A4" s="21" t="s">
+        <v>123</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="C5" s="7">
         <v>-2.5</v>
@@ -3501,18 +3501,18 @@
         <v>12</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>128</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>129</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
@@ -3521,75 +3521,75 @@
         <v>12</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="C7" s="7">
         <v>1.2250000000000001</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="C8" s="7">
         <v>1.2</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>142</v>
+      <c r="A10" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="F11" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -3642,8 +3642,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>147</v>
+      <c r="A1" s="22" t="s">
+        <v>146</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -3682,8 +3682,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>149</v>
+      <c r="A4" s="21" t="s">
+        <v>148</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3693,19 +3693,19 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -3713,19 +3713,19 @@
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>156</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>12</v>
@@ -3733,19 +3733,19 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>12</v>
@@ -3753,27 +3753,27 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>163</v>
       </c>
       <c r="C8" s="7">
         <v>5.8056599999999996</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>166</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3783,19 +3783,19 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>168</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>169</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>12</v>
@@ -3803,19 +3803,19 @@
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>12</v>
@@ -3823,19 +3823,19 @@
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>12</v>
@@ -3843,27 +3843,27 @@
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="C13" s="7">
         <v>5.2778799999999997</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>183</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -3873,19 +3873,19 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>186</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>12</v>
@@ -3893,70 +3893,70 @@
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>189</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="C17" s="7">
         <v>0</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="C18" s="7">
         <v>0</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="C19" s="7">
         <v>0.15</v>
@@ -3965,55 +3965,55 @@
         <v>89</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>207</v>
       </c>
       <c r="C20" s="7">
         <v>1.0491900000000001</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="C21" s="7">
         <v>1.76</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>214</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -4023,19 +4023,19 @@
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>216</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>217</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>12</v>
@@ -4043,19 +4043,19 @@
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>12</v>
@@ -4063,27 +4063,27 @@
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="C25" s="7">
         <v>5.2778799999999997</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F25" s="6" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
-        <v>227</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -4093,19 +4093,19 @@
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>12</v>
@@ -4113,19 +4113,19 @@
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>12</v>
@@ -4133,47 +4133,47 @@
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="C29" s="7">
         <v>3.6529410000000002</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>241</v>
       </c>
       <c r="C30" s="7">
         <v>4.3157699999999997</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E30" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
-        <v>243</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -4183,10 +4183,10 @@
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>245</v>
       </c>
       <c r="C32" s="7">
         <v>4.2000000000000003E-2</v>
@@ -4195,18 +4195,18 @@
         <v>89</v>
       </c>
       <c r="E32" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="C33" s="7">
         <v>-3.7999999999999999E-2</v>
@@ -4215,15 +4215,15 @@
         <v>89</v>
       </c>
       <c r="E33" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F33" s="6" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
-        <v>252</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -4233,19 +4233,19 @@
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>12</v>
@@ -4253,19 +4253,19 @@
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>12</v>
@@ -4273,27 +4273,27 @@
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="C37" s="7">
         <v>5.8304799999999997E-2</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="6" t="s">
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
-        <v>265</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -4303,19 +4303,19 @@
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>267</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>268</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>12</v>
@@ -4323,19 +4323,19 @@
     </row>
     <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>12</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="C41" s="7">
         <v>0.22806699999999999</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E41" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -4392,8 +4392,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>278</v>
+      <c r="A1" s="22" t="s">
+        <v>277</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -4403,7 +4403,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -4432,8 +4432,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>280</v>
+      <c r="A4" s="21" t="s">
+        <v>279</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -4443,19 +4443,19 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="C5" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -4463,19 +4463,19 @@
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>286</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>12</v>
@@ -4483,19 +4483,19 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>12</v>
@@ -4503,19 +4503,19 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>294</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>12</v>
@@ -4523,67 +4523,67 @@
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>296</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="C9" s="7">
         <v>30.96</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>302</v>
       </c>
       <c r="C10" s="7">
         <v>3</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>304</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="C11" s="7">
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
         <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>310</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -4593,39 +4593,39 @@
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>314</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>316</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>317</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>12</v>
@@ -4633,30 +4633,30 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>320</v>
       </c>
       <c r="C15" s="7">
         <v>19.792000000000002</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>323</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>324</v>
       </c>
       <c r="C16" s="7">
         <v>50</v>
@@ -4665,27 +4665,27 @@
         <v>38</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>325</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>329</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>12</v>
@@ -4693,50 +4693,50 @@
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>332</v>
       </c>
       <c r="C18" s="7">
         <v>0.18</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>334</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="C20" s="7">
         <v>1.3650000000000001E-2</v>
@@ -4745,27 +4745,27 @@
         <v>89</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>341</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>12</v>
@@ -4796,8 +4796,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>347</v>
+      <c r="A1" s="22" t="s">
+        <v>346</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -4836,8 +4836,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>349</v>
+      <c r="A4" s="21" t="s">
+        <v>348</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -4847,19 +4847,19 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>351</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>352</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -4867,19 +4867,19 @@
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>356</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>12</v>
@@ -4887,19 +4887,19 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>360</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>12</v>
@@ -4907,27 +4907,27 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>362</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>363</v>
       </c>
       <c r="C8" s="7">
         <v>5.8056599999999996</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>364</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>365</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -4937,19 +4937,19 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>368</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>12</v>
@@ -4957,19 +4957,19 @@
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>372</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>12</v>
@@ -4977,19 +4977,19 @@
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>375</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>376</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>12</v>
@@ -4997,27 +4997,27 @@
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>378</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>379</v>
       </c>
       <c r="C13" s="7">
         <v>5.2778799999999997</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>381</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -5027,87 +5027,87 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>383</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>384</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>387</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>388</v>
       </c>
       <c r="C16" s="7">
         <v>0</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>389</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="C17" s="7">
         <v>0</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E17" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>395</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>396</v>
       </c>
       <c r="C18" s="7">
         <v>1.0491900000000001</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
         <v>397</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>398</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -5117,19 +5117,19 @@
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>401</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>12</v>
@@ -5137,27 +5137,27 @@
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>405</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
         <v>406</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>407</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -5167,19 +5167,19 @@
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>409</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>410</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>12</v>
@@ -5187,19 +5187,19 @@
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>413</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>414</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>12</v>
@@ -5207,27 +5207,27 @@
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>416</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>417</v>
       </c>
       <c r="C25" s="7">
         <v>5.8304799999999997E-2</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>418</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
-        <v>419</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -5237,19 +5237,19 @@
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>421</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>422</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>12</v>
@@ -5257,19 +5257,19 @@
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>425</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>426</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>12</v>
@@ -5277,27 +5277,27 @@
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="C29" s="7">
         <v>0.22806699999999999</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
         <v>430</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
-        <v>431</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -5307,19 +5307,19 @@
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>12</v>
@@ -5327,19 +5327,19 @@
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>437</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>438</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>89</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>12</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>440</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>441</v>
       </c>
       <c r="C33" s="7">
         <v>2.5000000000000001E-2</v>
@@ -5359,18 +5359,18 @@
         <v>89</v>
       </c>
       <c r="E33" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>442</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="C34" s="7">
         <v>-4.4999999999999998E-2</v>
@@ -5379,15 +5379,15 @@
         <v>89</v>
       </c>
       <c r="E34" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="F34" s="8" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
-        <v>448</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -5397,69 +5397,69 @@
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>449</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>450</v>
       </c>
       <c r="C36" s="7">
         <v>76.72</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E36" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>451</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>453</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>454</v>
       </c>
       <c r="C37" s="7">
         <v>7</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="F37" s="6" t="s">
+    </row>
+    <row r="38" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>89</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>90</v>
@@ -5467,10 +5467,10 @@
     </row>
     <row r="40" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="C40" s="3">
         <v>0.15</v>
@@ -5479,127 +5479,127 @@
         <v>89</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>465</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>466</v>
       </c>
       <c r="C41" s="3">
         <v>1.76</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E41" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="F41" s="15" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33" t="s">
-        <v>468</v>
-      </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
     </row>
     <row r="43" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="B43" s="15" t="s">
         <v>469</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>470</v>
       </c>
       <c r="C43" s="3">
         <v>0.3</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>473</v>
       </c>
       <c r="C44" s="3">
         <v>3.6529410000000002</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="B45" s="15" t="s">
         <v>475</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>476</v>
       </c>
       <c r="C45" s="3">
         <v>4.3157699999999997</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E45" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="30" t="s">
         <v>477</v>
       </c>
-      <c r="F45" s="15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
     </row>
     <row r="47" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>480</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>89</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>12</v>
@@ -5607,19 +5607,19 @@
     </row>
     <row r="48" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>89</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>12</v>
@@ -5627,19 +5627,19 @@
     </row>
     <row r="49" spans="1:6" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>486</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="C49" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>89</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>12</v>
@@ -5647,19 +5647,19 @@
     </row>
     <row r="50" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>89</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>12</v>
@@ -5667,26 +5667,31 @@
     </row>
     <row r="51" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>494</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>495</v>
       </c>
       <c r="C51" s="3">
         <v>1.5</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A4:F4"/>
@@ -5695,11 +5700,6 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5719,8 +5719,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>497</v>
+      <c r="A1" s="22" t="s">
+        <v>496</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -5759,8 +5759,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>499</v>
+      <c r="A4" s="21" t="s">
+        <v>498</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -5770,50 +5770,50 @@
     </row>
     <row r="5" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>502</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="C6" s="7">
         <v>43780</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>662</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>506</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>663</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>509</v>
       </c>
       <c r="C7" s="7">
         <v>0.01</v>
@@ -5822,33 +5822,33 @@
         <v>89</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>660</v>
+        <v>657</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>655</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>656</v>
       </c>
       <c r="C8" s="7">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>659</v>
-      </c>
-      <c r="F8" s="35"/>
+        <v>658</v>
+      </c>
+      <c r="F8" s="32"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>510</v>
+      <c r="A9" s="21" t="s">
+        <v>509</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -5858,50 +5858,50 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>502</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>514</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>515</v>
       </c>
       <c r="C11" s="7">
         <v>30650</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>517</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>518</v>
       </c>
       <c r="C12" s="7">
         <v>0.01</v>
@@ -5910,33 +5910,33 @@
         <v>89</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>660</v>
+        <v>657</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C13" s="7">
         <v>0</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>659</v>
-      </c>
-      <c r="F13" s="35"/>
+        <v>658</v>
+      </c>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>519</v>
+      <c r="A14" s="21" t="s">
+        <v>518</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -5946,87 +5946,87 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>521</v>
-      </c>
       <c r="C15" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>502</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>664</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>522</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>523</v>
       </c>
       <c r="C16" s="7">
         <v>5000</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>665</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>526</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>527</v>
       </c>
       <c r="C17" s="7">
         <v>1000000</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>529</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>530</v>
       </c>
       <c r="C18" s="7">
         <v>1000000</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
         <v>531</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>532</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -6036,82 +6036,82 @@
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>502</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>536</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>537</v>
       </c>
       <c r="C21" s="7">
         <v>5000</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>524</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C22" s="7">
         <v>1000000</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C23" s="7">
         <v>1000000</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -6143,8 +6143,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
-        <v>539</v>
+      <c r="A1" s="22" t="s">
+        <v>538</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -6154,7 +6154,7 @@
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6183,8 +6183,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>541</v>
+      <c r="A4" s="21" t="s">
+        <v>540</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6194,79 +6194,79 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>545</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>550</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>552</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>553</v>
       </c>
       <c r="C7" s="7">
         <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>556</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>557</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>12</v>
@@ -6274,139 +6274,139 @@
     </row>
     <row r="9" spans="1:6" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>562</v>
-      </c>
       <c r="F9" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>563</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>564</v>
       </c>
       <c r="C10" s="7">
         <v>0.01</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="F10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>570</v>
-      </c>
       <c r="F12" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>573</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>574</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="C14" s="7">
         <v>10</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
     </row>
     <row r="16" spans="1:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>579</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>580</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>12</v>
@@ -6414,42 +6414,42 @@
     </row>
     <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>561</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="13" t="s">
         <v>584</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>586</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>587</v>
       </c>
       <c r="C18" s="12">
         <v>0.01</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>565</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -6478,7 +6478,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -6518,7 +6518,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="20"/>
@@ -6568,7 +6568,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="21" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="20"/>
@@ -6658,7 +6658,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="21" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="20"/>
@@ -6688,7 +6688,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="20"/>
@@ -6778,7 +6778,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="21" t="s">
         <v>68</v>
       </c>
       <c r="B19" s="20"/>
